--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2024_la_araucania.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2024_la_araucania.xlsx
@@ -1016,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1025,150 +1025,103 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Angol</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>359104.66</v>
+          <t>Cholchol</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Carahue</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>197158</v>
+          <t>Cunco</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cholchol</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>192808.33</v>
+          <t>Freire</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Collipulli</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>283378.78</v>
+          <t>Galvarino</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cunco</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>202108.62</v>
+          <t>Nueva Imperial</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Curacautín</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>232341.02</v>
+          <t>Perquenco</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Curarrehue</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>177979.33</v>
+          <t>Pitrufquén</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ercilla</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>183653.78</v>
+          <t>Temuco</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Freire</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>246749.39</v>
+          <t>Teodoro Schmidt</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Galvarino</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>216703.45</v>
+          <t>Vilcún</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gorbea</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>220304.45</v>
+          <t>Angol</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lautaro</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>297393.97</v>
+          <t>Collipulli</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Loncoche</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>252908.72</v>
+          <t>Curacautín</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lonquimay</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>199510.45</v>
+          <t>Ercilla</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1177,9 +1130,6 @@
           <t>Los Sauces</t>
         </is>
       </c>
-      <c r="B16">
-        <v>215405.11</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1187,168 +1137,117 @@
           <t>Lumaco</t>
         </is>
       </c>
-      <c r="B17">
-        <v>200027.27</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Melipeuco</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>217579.39</v>
+          <t>Purén</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nueva Imperial</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>229399.81</v>
+          <t>Renaico</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Padre Las Casas</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>278254</v>
+          <t>Traiguén</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Perquenco</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>235549.11</v>
+          <t>Victoria</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pitrufquén</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>273298.81</v>
+          <t>Gorbea</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pucón</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>293731.81</v>
+          <t>Lautaro</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Purén</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>231554.05</v>
+          <t>Lonquimay</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Renaico</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>329717.12</v>
+          <t>Carahue</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Saavedra</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>157006.56</v>
+          <t>Toltén</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Temuco</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>432040.25</v>
+          <t>Loncoche</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Teodoro Schmidt</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>170897.05</v>
+          <t>Curarrehue</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Toltén</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>201504.44</v>
+          <t>Saavedra</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Traiguén</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>241455.2</v>
+          <t>Villarrica</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>288613.34</v>
+          <t>Pucón</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Vilcún</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>269694.84</v>
+          <t>Padre Las Casas</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Villarrica</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>292740.59</v>
+          <t>Melipeuco</t>
+        </is>
       </c>
     </row>
   </sheetData>
